--- a/excel-files/CALOOCAN/NHC HIGH SCHOOL.xlsx
+++ b/excel-files/CALOOCAN/NHC HIGH SCHOOL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29803"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29816"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jonathan Buquia\Downloads\OFFICE\SEMINARS\Workshop on the Strengthened Regional Inventory of Learning Resources\SCHOOLS in NCR\CALOOCAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="460" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D798C46B-97AD-4AD1-8D74-1D1D7B1C70AA}"/>
+  <xr:revisionPtr revIDLastSave="520" documentId="13_ncr:1_{BFB59F67-F0DC-4675-A682-EB0734A8026A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{51C755C4-FB1D-4BAE-AE0E-14DE30496DE4}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="TextBooks" sheetId="1" r:id="rId1"/>
@@ -3751,7 +3751,7 @@
       </c>
       <c r="I2" s="6"/>
     </row>
-    <row r="3" spans="1:9" ht="42.75" hidden="1" customHeight="1">
+    <row r="3" spans="1:9" ht="42.75" customHeight="1">
       <c r="A3" s="1">
         <v>1</v>
       </c>
@@ -3771,7 +3771,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="29.25" hidden="1" customHeight="1">
+    <row r="4" spans="1:9" ht="29.25" customHeight="1">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -3791,7 +3791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:9" ht="21" hidden="1" customHeight="1">
+    <row r="5" spans="1:9" ht="21" customHeight="1">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -3811,7 +3811,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="25.5" hidden="1" customHeight="1">
+    <row r="6" spans="1:9" ht="25.5" customHeight="1">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -3831,7 +3831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:9" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -3851,12 +3851,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9" hidden="1">
+    <row r="8" spans="1:9">
       <c r="C8" s="6"/>
       <c r="D8" s="6"/>
       <c r="E8" s="6"/>
     </row>
-    <row r="9" spans="1:9" ht="39.75" hidden="1" customHeight="1">
+    <row r="9" spans="1:9" ht="39.75" customHeight="1">
       <c r="A9" s="1">
         <v>2</v>
       </c>
@@ -3876,7 +3876,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="29.25" hidden="1" customHeight="1">
+    <row r="10" spans="1:9" ht="29.25" customHeight="1">
       <c r="A10" s="1">
         <v>2</v>
       </c>
@@ -3896,7 +3896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="28.5" hidden="1" customHeight="1">
+    <row r="11" spans="1:9" ht="28.5" customHeight="1">
       <c r="A11" s="1">
         <v>2</v>
       </c>
@@ -3916,7 +3916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="24" hidden="1" customHeight="1">
+    <row r="12" spans="1:9" ht="24" customHeight="1">
       <c r="A12" s="1">
         <v>2</v>
       </c>
@@ -3936,7 +3936,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:9" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -3956,12 +3956,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:9" hidden="1">
+    <row r="14" spans="1:9">
       <c r="C14" s="6"/>
       <c r="D14" s="6"/>
       <c r="E14" s="6"/>
     </row>
-    <row r="15" spans="1:9" ht="49.5" hidden="1" customHeight="1">
+    <row r="15" spans="1:9" ht="49.5" customHeight="1">
       <c r="A15" s="1">
         <v>3</v>
       </c>
@@ -3981,7 +3981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:9" ht="29.25" hidden="1" customHeight="1">
+    <row r="16" spans="1:9" ht="29.25" customHeight="1">
       <c r="A16" s="1">
         <v>3</v>
       </c>
@@ -4001,7 +4001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="17" spans="1:8" ht="27" customHeight="1">
       <c r="A17" s="1">
         <v>3</v>
       </c>
@@ -4021,7 +4021,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:8" ht="23.25" hidden="1" customHeight="1">
+    <row r="18" spans="1:8" ht="23.25" customHeight="1">
       <c r="A18" s="1">
         <v>3</v>
       </c>
@@ -4041,7 +4041,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:8" ht="21" hidden="1" customHeight="1">
+    <row r="19" spans="1:8" ht="21" customHeight="1">
       <c r="A19" s="1">
         <v>3</v>
       </c>
@@ -4061,7 +4061,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:8" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>3</v>
       </c>
@@ -4081,7 +4081,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:8" hidden="1">
+    <row r="21" spans="1:8">
       <c r="A21" s="7"/>
       <c r="B21" s="7"/>
       <c r="C21" s="8"/>
@@ -4091,7 +4091,7 @@
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
     </row>
-    <row r="22" spans="1:8" ht="28.5" hidden="1" customHeight="1">
+    <row r="22" spans="1:8" ht="28.5" customHeight="1">
       <c r="A22" s="1">
         <v>4</v>
       </c>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:8" ht="24" hidden="1" customHeight="1">
+    <row r="23" spans="1:8" ht="24" customHeight="1">
       <c r="A23" s="1">
         <v>4</v>
       </c>
@@ -4131,7 +4131,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:8" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:8" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>4</v>
       </c>
@@ -4151,7 +4151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:8" ht="27" hidden="1" customHeight="1">
+    <row r="25" spans="1:8" ht="27" customHeight="1">
       <c r="A25" s="1">
         <v>4</v>
       </c>
@@ -4171,7 +4171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="26" spans="1:8" ht="33.75" customHeight="1">
       <c r="A26" s="1">
         <v>4</v>
       </c>
@@ -4191,7 +4191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="27" spans="1:8" ht="33.75" customHeight="1">
       <c r="A27" s="1">
         <v>4</v>
       </c>
@@ -4211,7 +4211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:8" ht="33.75" hidden="1" customHeight="1">
+    <row r="28" spans="1:8" ht="33.75" customHeight="1">
       <c r="A28" s="1">
         <v>4</v>
       </c>
@@ -4231,7 +4231,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="29" spans="1:8" ht="27.75" customHeight="1">
       <c r="A29" s="1">
         <v>4</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="30" spans="1:8" ht="27.75" customHeight="1">
       <c r="A30" s="1">
         <v>4</v>
       </c>
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="31" spans="1:8" ht="27.75" customHeight="1">
       <c r="A31" s="7"/>
       <c r="B31" s="7"/>
       <c r="C31" s="8"/>
@@ -4281,7 +4281,7 @@
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
     </row>
-    <row r="32" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="32" spans="1:8" ht="27.75" customHeight="1">
       <c r="A32" s="1">
         <v>5</v>
       </c>
@@ -4301,7 +4301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="33" spans="1:8" ht="27.75" customHeight="1">
       <c r="A33" s="1">
         <v>5</v>
       </c>
@@ -4321,7 +4321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="34" spans="1:8" ht="27.75" customHeight="1">
       <c r="A34" s="1">
         <v>5</v>
       </c>
@@ -4341,7 +4341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="35" spans="1:8" ht="27.75" customHeight="1">
       <c r="A35" s="1">
         <v>5</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:8" ht="39" hidden="1" customHeight="1">
+    <row r="36" spans="1:8" ht="39" customHeight="1">
       <c r="A36" s="1">
         <v>5</v>
       </c>
@@ -4381,7 +4381,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="37" spans="1:8" ht="27.75" customHeight="1">
       <c r="A37" s="1">
         <v>5</v>
       </c>
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="38" spans="1:8" ht="27.75" customHeight="1">
       <c r="A38" s="1">
         <v>5</v>
       </c>
@@ -4421,7 +4421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="39" spans="1:8" ht="27.75" customHeight="1">
       <c r="A39" s="1">
         <v>5</v>
       </c>
@@ -4441,7 +4441,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="40" spans="1:8" ht="27.75" customHeight="1">
       <c r="A40" s="1">
         <v>5</v>
       </c>
@@ -4461,7 +4461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="41" spans="1:8" ht="27.75" customHeight="1">
       <c r="A41" s="7"/>
       <c r="B41" s="7"/>
       <c r="C41" s="8"/>
@@ -4471,7 +4471,7 @@
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
     </row>
-    <row r="42" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="42" spans="1:8" ht="27.75" customHeight="1">
       <c r="A42" s="1">
         <v>6</v>
       </c>
@@ -4491,7 +4491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="43" spans="1:8" ht="27.75" customHeight="1">
       <c r="A43" s="1">
         <v>6</v>
       </c>
@@ -4511,7 +4511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="44" spans="1:8" ht="27.75" customHeight="1">
       <c r="A44" s="1">
         <v>6</v>
       </c>
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="45" spans="1:8" ht="27.75" customHeight="1">
       <c r="A45" s="1">
         <v>6</v>
       </c>
@@ -4551,7 +4551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:8" ht="36.75" hidden="1" customHeight="1">
+    <row r="46" spans="1:8" ht="36.75" customHeight="1">
       <c r="A46" s="1">
         <v>6</v>
       </c>
@@ -4571,7 +4571,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="47" spans="1:8" ht="27.75" customHeight="1">
       <c r="A47" s="1">
         <v>6</v>
       </c>
@@ -4591,7 +4591,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="48" spans="1:8" ht="27.75" customHeight="1">
       <c r="A48" s="1">
         <v>6</v>
       </c>
@@ -4611,7 +4611,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="49" spans="1:8" ht="27.75" customHeight="1">
       <c r="A49" s="1">
         <v>6</v>
       </c>
@@ -4631,7 +4631,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="50" spans="1:8" ht="27.75" customHeight="1">
       <c r="A50" s="1">
         <v>6</v>
       </c>
@@ -4651,7 +4651,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:8" ht="27.75" hidden="1" customHeight="1">
+    <row r="51" spans="1:8" ht="27.75" customHeight="1">
       <c r="A51" s="7"/>
       <c r="B51" s="7"/>
       <c r="C51" s="8"/>
@@ -5889,12 +5889,15 @@
     <mergeCell ref="A1:H1"/>
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
-  <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15:E20 E22:E30 E32:E40 E52:E60 E62:E70 E42:E50 E3:E7 E72:E80 E82:E90 E9:E13 E92:E99" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
+  <dataValidations count="3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E15:E20 E22:E30 E32:E40 E3:E7 E9:E13 E42:E50" xr:uid="{B46E7B13-721E-4D49-837E-C02BF9777D48}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F15:F20 F22:F30 F32:F40 F42:F50 F52:F60 F62:F70 F72:F80 F82:F90 F3:F7 F9:F13 F92:F99" xr:uid="{2F7388E0-D1A1-4571-8C10-96CB9A727EB3}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E92:E99 E82:E90 E72:E80 E62:E70 E52:E60" xr:uid="{8240E74A-CB6A-4C0D-9BA2-8C5FD1606948}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6087,7 +6090,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="30.6" hidden="1" customHeight="1">
+    <row r="4" spans="1:27" ht="30.6" customHeight="1">
       <c r="A4" s="39" t="s">
         <v>74</v>
       </c>
@@ -6154,7 +6157,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J5" s="13"/>
       <c r="N5" s="13"/>
       <c r="O5" s="13"/>
@@ -6166,7 +6169,7 @@
       <c r="Z5" s="13"/>
       <c r="AA5" s="13"/>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -6235,7 +6238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -6304,7 +6307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -6373,7 +6376,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -6442,7 +6445,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -6511,7 +6514,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -6580,7 +6583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" ht="19.149999999999999">
       <c r="A12" s="1">
         <v>1</v>
       </c>
@@ -6649,7 +6652,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>1</v>
       </c>
@@ -6718,7 +6721,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J14" s="13"/>
       <c r="N14" s="13"/>
       <c r="O14" s="13"/>
@@ -6731,7 +6734,7 @@
       <c r="Z14" s="13"/>
       <c r="AA14" s="13"/>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="38.25">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -6800,7 +6803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -6869,7 +6872,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -6938,7 +6941,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -7007,7 +7010,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -7076,7 +7079,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -7145,7 +7148,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" ht="19.149999999999999">
       <c r="A21" s="1">
         <v>2</v>
       </c>
@@ -7214,7 +7217,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>2</v>
       </c>
@@ -7283,7 +7286,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J23" s="13"/>
       <c r="M23" s="5"/>
       <c r="N23" s="13"/>
@@ -7297,7 +7300,7 @@
       <c r="Z23" s="13"/>
       <c r="AA23" s="13"/>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -7366,7 +7369,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -7435,7 +7438,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -7504,7 +7507,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -7573,7 +7576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -7642,7 +7645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -7711,7 +7714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -7780,7 +7783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" ht="19.149999999999999">
       <c r="A31" s="1">
         <v>3</v>
       </c>
@@ -7849,7 +7852,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>3</v>
       </c>
@@ -7918,7 +7921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J33" s="13"/>
       <c r="M33" s="5"/>
       <c r="N33" s="13"/>
@@ -7932,7 +7935,7 @@
       <c r="Z33" s="13"/>
       <c r="AA33" s="13"/>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -8001,7 +8004,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -8070,7 +8073,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.5">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -8139,7 +8142,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -8208,7 +8211,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="1">
         <v>4</v>
       </c>
@@ -8277,7 +8280,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -8346,7 +8349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -8415,7 +8418,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="1">
         <v>4</v>
       </c>
@@ -8484,7 +8487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" ht="19.149999999999999">
       <c r="A42" s="1">
         <v>4</v>
       </c>
@@ -8553,7 +8556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J43" s="13"/>
       <c r="M43" s="5"/>
       <c r="N43" s="13"/>
@@ -8567,7 +8570,7 @@
       <c r="Z43" s="13"/>
       <c r="AA43" s="13"/>
     </row>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -8636,7 +8639,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -8705,7 +8708,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -8774,7 +8777,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -8843,7 +8846,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -8912,7 +8915,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="49" spans="1:27" ht="19.149999999999999">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -8981,7 +8984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="1">
         <v>5</v>
       </c>
@@ -9050,7 +9053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -9119,7 +9122,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" ht="19.149999999999999">
       <c r="A52" s="1">
         <v>5</v>
       </c>
@@ -9188,7 +9191,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J53" s="13"/>
       <c r="M53" s="5"/>
       <c r="N53" s="13"/>
@@ -9202,7 +9205,7 @@
       <c r="Z53" s="13"/>
       <c r="AA53" s="13"/>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>6</v>
       </c>
@@ -9271,7 +9274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" ht="19.149999999999999">
       <c r="A55" s="1">
         <v>6</v>
       </c>
@@ -9340,7 +9343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -9409,7 +9412,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -9478,7 +9481,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -9547,7 +9550,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -9616,7 +9619,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -9685,7 +9688,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -9754,7 +9757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="1">
         <v>6</v>
       </c>
@@ -9823,7 +9826,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" s="7" customFormat="1" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" s="7" customFormat="1" ht="19.149999999999999">
       <c r="J63" s="13"/>
       <c r="M63" s="5"/>
       <c r="N63" s="13"/>
@@ -13655,8 +13658,8 @@
     <mergeCell ref="V2:AA2"/>
     <mergeCell ref="A1:AA1"/>
   </mergeCells>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X24:X32 X34:X42 X44:X52 X64:X72 X74:X82 X54:X62 X84:X92 X94:X102 X15:X22 X6:X13 L24:L32 L34:L42 L44:L52 L64:L72 L74:L82 L54:L62 L84:L92 L94:L102 L15:L22 L6:L13 R24:R32 R34:R42 R44:R52 R64:R72 R74:R82 R54:R62 R84:R92 R94:R102 R15:R22 R6:R13 F24:F32 F34:F42 F44:F52 F64:F72 F54:F62 F6:F13 F84:F92 F94:F102 F15:F22 F104:F111 R104:R111 L104:L111 X104:X111 F74:F82 X113:X128 F113:F128 R113:R128 L113:L128" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
+  <dataValidations count="4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R113:R128 X113:X128 L113:L128 F113:F128" xr:uid="{4ECCD083-8EC4-42EE-B46C-B614411F330D}">
       <formula1>"2024,2025"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="M15:M111 Y15:Y111 S5:S111 G6:G13 M6:M13 Y6:Y13 G15:G22 G24:G32 G34:G42 G44:G52 G54:G62 G64:G72 G104:G111 G84:G92 G94:G102 G74:G82" xr:uid="{5129D80C-83DF-45BE-B6AD-F21CA596CBA5}">
@@ -13664,6 +13667,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Y113:Y128 M113:M128 S113:S128 K119:K123 G113:G118 G124:G128" xr:uid="{8289B4A9-982E-4C7E-A8E2-4BF3404561DB}">
       <formula1>"CO,RO,SDO"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F104:F111 F94:F102 F84:F92 F74:F82 F64:F72 F54:F62 F44:F52 F34:F42 F24:F32 F15:F22 F6:F13 L104:L111 L94:L102 L84:L91 L74:L82 L64:L72 L54:L62 L44:L52 L35:L42 L24:L32 L15:L22 L6:L13 L92 L34 R104:R111 R94:R102 R84:R92 R74:R82 R64:R72 R54:R62 R44:R52 R34:R42 R24:R32 R15:R22 R6:R13 X104:X111 X94:X102 X84:X92 X74:X82 X64:X72 X54:X62 X44:X52 X34:X42 X24:X32 X15:X22 X6:X13" xr:uid="{CACD4148-3069-4061-BD89-3385D4210038}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13682,10 +13688,10 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AA171"/>
+  <dimension ref="A1:AA146"/>
   <sheetFormatPr defaultRowHeight="13.9"/>
   <cols>
-    <col min="1" max="1" width="9.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" customWidth="1"/>
     <col min="2" max="2" width="28.5703125" customWidth="1"/>
     <col min="3" max="3" width="17.140625" customWidth="1"/>
     <col min="4" max="4" width="16.42578125" customWidth="1"/>
@@ -13859,7 +13865,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="38.25" hidden="1">
+    <row r="4" spans="1:27" ht="38.25">
       <c r="A4" s="1">
         <v>1</v>
       </c>
@@ -13928,7 +13934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="5" spans="1:27" ht="19.149999999999999">
       <c r="A5" s="1">
         <v>1</v>
       </c>
@@ -13997,7 +14003,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="6" spans="1:27" ht="19.149999999999999">
       <c r="A6" s="1">
         <v>1</v>
       </c>
@@ -14066,7 +14072,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="7" spans="1:27" ht="19.149999999999999">
       <c r="A7" s="1">
         <v>1</v>
       </c>
@@ -14135,7 +14141,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="8" spans="1:27" ht="19.149999999999999">
       <c r="A8" s="1">
         <v>1</v>
       </c>
@@ -14204,7 +14210,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="9" spans="1:27" ht="19.149999999999999">
       <c r="A9" s="1">
         <v>1</v>
       </c>
@@ -14273,7 +14279,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="10" spans="1:27" ht="19.149999999999999">
       <c r="A10" s="1">
         <v>1</v>
       </c>
@@ -14342,7 +14348,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="11" spans="1:27" ht="19.149999999999999">
       <c r="A11" s="1">
         <v>1</v>
       </c>
@@ -14411,8 +14417,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="13" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="12" spans="1:27" s="7" customFormat="1"/>
+    <row r="13" spans="1:27" ht="19.149999999999999">
       <c r="A13" s="1">
         <v>2</v>
       </c>
@@ -14481,7 +14487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="14" spans="1:27" ht="19.149999999999999">
       <c r="A14" s="1">
         <v>2</v>
       </c>
@@ -14550,7 +14556,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="15" spans="1:27" ht="19.149999999999999">
       <c r="A15" s="1">
         <v>2</v>
       </c>
@@ -14619,7 +14625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="16" spans="1:27" ht="19.149999999999999">
       <c r="A16" s="1">
         <v>2</v>
       </c>
@@ -14688,7 +14694,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="17" spans="1:27" ht="19.149999999999999">
       <c r="A17" s="1">
         <v>2</v>
       </c>
@@ -14757,7 +14763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="18" spans="1:27" ht="19.149999999999999">
       <c r="A18" s="1">
         <v>2</v>
       </c>
@@ -14826,7 +14832,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="19" spans="1:27" ht="19.149999999999999">
       <c r="A19" s="1">
         <v>2</v>
       </c>
@@ -14895,7 +14901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="20" spans="1:27" ht="19.149999999999999">
       <c r="A20" s="1">
         <v>2</v>
       </c>
@@ -14964,8 +14970,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="22" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="21" spans="1:27" s="7" customFormat="1"/>
+    <row r="22" spans="1:27" ht="19.149999999999999">
       <c r="A22" s="1">
         <v>3</v>
       </c>
@@ -15034,7 +15040,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="23" spans="1:27" ht="19.149999999999999">
       <c r="A23" s="1">
         <v>3</v>
       </c>
@@ -15103,7 +15109,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="24" spans="1:27" ht="19.149999999999999">
       <c r="A24" s="1">
         <v>3</v>
       </c>
@@ -15172,7 +15178,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="25" spans="1:27" ht="19.149999999999999">
       <c r="A25" s="1">
         <v>3</v>
       </c>
@@ -15241,7 +15247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="26" spans="1:27" ht="19.149999999999999">
       <c r="A26" s="1">
         <v>3</v>
       </c>
@@ -15310,7 +15316,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="27" spans="1:27" ht="19.149999999999999">
       <c r="A27" s="1">
         <v>3</v>
       </c>
@@ -15379,7 +15385,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="28" spans="1:27" ht="19.149999999999999">
       <c r="A28" s="1">
         <v>3</v>
       </c>
@@ -15448,7 +15454,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="29" spans="1:27" ht="19.149999999999999">
       <c r="A29" s="1">
         <v>3</v>
       </c>
@@ -15517,7 +15523,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="30" spans="1:27" ht="19.149999999999999">
       <c r="A30" s="1">
         <v>3</v>
       </c>
@@ -15586,8 +15592,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="32" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="31" spans="1:27" s="7" customFormat="1"/>
+    <row r="32" spans="1:27" ht="19.149999999999999">
       <c r="A32" s="1">
         <v>4</v>
       </c>
@@ -15656,7 +15662,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="33" spans="1:27" ht="19.149999999999999">
       <c r="A33" s="1">
         <v>4</v>
       </c>
@@ -15725,7 +15731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="34" spans="1:27" ht="19.149999999999999">
       <c r="A34" s="1">
         <v>4</v>
       </c>
@@ -15794,7 +15800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="35" spans="1:27" ht="19.149999999999999">
       <c r="A35" s="1">
         <v>4</v>
       </c>
@@ -15863,7 +15869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="36" spans="1:27" ht="19.149999999999999">
       <c r="A36" s="1">
         <v>4</v>
       </c>
@@ -15932,7 +15938,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="37" spans="1:27" ht="19.149999999999999">
       <c r="A37" s="1">
         <v>4</v>
       </c>
@@ -16001,7 +16007,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="38" spans="1:27" ht="19.149999999999999">
       <c r="A38" s="37">
         <v>4</v>
       </c>
@@ -16070,7 +16076,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="39" spans="1:27" ht="19.149999999999999">
       <c r="A39" s="1">
         <v>4</v>
       </c>
@@ -16139,7 +16145,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="40" spans="1:27" ht="19.149999999999999">
       <c r="A40" s="1">
         <v>4</v>
       </c>
@@ -16208,7 +16214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="41" spans="1:27" ht="19.149999999999999">
       <c r="A41" s="37">
         <v>4</v>
       </c>
@@ -16277,7 +16283,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="42" spans="1:27" ht="19.149999999999999">
       <c r="A42" s="1">
         <v>4</v>
       </c>
@@ -16346,8 +16352,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="44" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="43" spans="1:27" s="7" customFormat="1"/>
+    <row r="44" spans="1:27" ht="19.149999999999999">
       <c r="A44" s="1">
         <v>5</v>
       </c>
@@ -16416,7 +16422,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="45" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="45" spans="1:27" ht="19.149999999999999">
       <c r="A45" s="1">
         <v>5</v>
       </c>
@@ -16485,7 +16491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="46" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="46" spans="1:27" ht="19.149999999999999">
       <c r="A46" s="1">
         <v>5</v>
       </c>
@@ -16554,7 +16560,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="47" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="47" spans="1:27" ht="19.149999999999999">
       <c r="A47" s="1">
         <v>5</v>
       </c>
@@ -16623,7 +16629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="48" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="48" spans="1:27" ht="19.149999999999999">
       <c r="A48" s="1">
         <v>5</v>
       </c>
@@ -16692,7 +16698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="49" spans="1:27" ht="19.5" hidden="1">
+    <row r="49" spans="1:27" ht="19.5">
       <c r="A49" s="1">
         <v>5</v>
       </c>
@@ -16761,7 +16767,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="50" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="50" spans="1:27" ht="19.149999999999999">
       <c r="A50" s="37">
         <v>5</v>
       </c>
@@ -16830,7 +16836,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="51" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="51" spans="1:27" ht="19.149999999999999">
       <c r="A51" s="1">
         <v>5</v>
       </c>
@@ -16899,7 +16905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="52" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="52" spans="1:27" ht="19.149999999999999">
       <c r="A52" s="1">
         <v>5</v>
       </c>
@@ -16968,7 +16974,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="53" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="53" spans="1:27" ht="19.149999999999999">
       <c r="A53" s="37">
         <v>5</v>
       </c>
@@ -17037,7 +17043,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="54" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="54" spans="1:27" ht="19.149999999999999">
       <c r="A54" s="1">
         <v>5</v>
       </c>
@@ -17106,8 +17112,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="55" spans="1:27" s="7" customFormat="1" hidden="1"/>
-    <row r="56" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="55" spans="1:27" s="7" customFormat="1"/>
+    <row r="56" spans="1:27" ht="19.149999999999999">
       <c r="A56" s="1">
         <v>6</v>
       </c>
@@ -17176,7 +17182,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="57" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="57" spans="1:27" ht="19.149999999999999">
       <c r="A57" s="1">
         <v>6</v>
       </c>
@@ -17245,7 +17251,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="58" spans="1:27" ht="19.149999999999999">
       <c r="A58" s="1">
         <v>6</v>
       </c>
@@ -17314,7 +17320,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="59" spans="1:27" ht="19.149999999999999">
       <c r="A59" s="1">
         <v>6</v>
       </c>
@@ -17383,7 +17389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="60" spans="1:27" ht="19.149999999999999">
       <c r="A60" s="1">
         <v>6</v>
       </c>
@@ -17452,7 +17458,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="61" spans="1:27" ht="19.149999999999999">
       <c r="A61" s="1">
         <v>6</v>
       </c>
@@ -17521,7 +17527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="62" spans="1:27" ht="19.149999999999999">
       <c r="A62" s="37">
         <v>6</v>
       </c>
@@ -17590,7 +17596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="63" spans="1:27" ht="19.149999999999999">
       <c r="A63" s="1">
         <v>6</v>
       </c>
@@ -17659,7 +17665,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="64" spans="1:27" ht="19.149999999999999">
       <c r="A64" s="1">
         <v>6</v>
       </c>
@@ -17728,7 +17734,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="65" spans="1:27" ht="19.149999999999999">
       <c r="A65" s="37">
         <v>6</v>
       </c>
@@ -17797,7 +17803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:27" ht="19.149999999999999" hidden="1">
+    <row r="66" spans="1:27" ht="19.5">
       <c r="A66" s="1">
         <v>6</v>
       </c>
@@ -17866,8 +17872,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:27" s="7" customFormat="1"/>
-    <row r="68" spans="1:27" ht="19.5">
+    <row r="67" spans="1:27" s="7" customFormat="1" ht="12.75" customHeight="1"/>
+    <row r="68" spans="1:27" ht="28.5" customHeight="1">
       <c r="A68" s="10">
         <v>7</v>
       </c>
@@ -21992,186 +21998,11 @@
     </row>
     <row r="140" spans="5:11" s="63" customFormat="1"/>
     <row r="141" spans="5:11" s="63" customFormat="1"/>
-    <row r="142" spans="5:11" s="63" customFormat="1">
-      <c r="J142" s="63" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="143" spans="5:11" s="63" customFormat="1">
-      <c r="J143" s="63" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="144" spans="5:11" s="63" customFormat="1">
-      <c r="J144" s="63" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="145" spans="10:10" s="63" customFormat="1">
-      <c r="J145" s="63" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="146" spans="10:10" s="63" customFormat="1">
-      <c r="J146" s="63" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="147" spans="10:10">
-      <c r="J147" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="148" spans="10:10">
-      <c r="J148" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="149" spans="10:10">
-      <c r="J149" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="150" spans="10:10">
-      <c r="J150" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="151" spans="10:10">
-      <c r="J151" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="152" spans="10:10">
-      <c r="J152" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="153" spans="10:10">
-      <c r="J153" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="154" spans="10:10">
-      <c r="J154" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="155" spans="10:10">
-      <c r="J155" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="156" spans="10:10">
-      <c r="J156" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="157" spans="10:10">
-      <c r="J157" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="158" spans="10:10">
-      <c r="J158" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="159" spans="10:10">
-      <c r="J159" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="160" spans="10:10">
-      <c r="J160" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="161" spans="10:10">
-      <c r="J161" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="162" spans="10:10">
-      <c r="J162" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="163" spans="10:10">
-      <c r="J163" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="164" spans="10:10">
-      <c r="J164" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="165" spans="10:10">
-      <c r="J165" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="166" spans="10:10">
-      <c r="J166" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="167" spans="10:10">
-      <c r="J167" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="168" spans="10:10">
-      <c r="J168" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="169" spans="10:10">
-      <c r="J169" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="170" spans="10:10">
-      <c r="J170" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
-    <row r="171" spans="10:10">
-      <c r="J171" t="e">
-        <f>#REF!*8</f>
-        <v>#REF!</v>
-      </c>
-    </row>
+    <row r="142" spans="5:11" s="63" customFormat="1"/>
+    <row r="143" spans="5:11" s="63" customFormat="1"/>
+    <row r="144" spans="5:11" s="63" customFormat="1"/>
+    <row r="145" s="63" customFormat="1"/>
+    <row r="146" s="63" customFormat="1"/>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="C3:C11 C13:C20 C22:C30 C32:C42 C44:C54 C56:C66 C68:C78 C80:C90 C92:C102 C104:C114 C116:C123" name="Textbooks"/>
@@ -22190,8 +22021,8 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="S116:S123 Y116:Y123 G116:G123 Y4:Y11 S4:S11 M4:M11 G4:G11 G13:G20 Y13:Y20 S13:S20 M13:M20 M22:M30 G22:G30 Y22:Y30 S22:S30 S32:S42 M32:M42 G32:G42 Y32:Y42 Y44:Y54 S44:S54 M44:M54 G44:G54 G56:G66 Y56:Y66 S56:S66 M56:M66 M68:M78 G68:G78 Y68:Y78 S68:S78 S80:S90 M80:M90 G80:G90 Y80:Y90 G92:G102 Y104:Y114 S92:S102 M92:M102 G104:G114 M116:M123 S104:S114 M104:M114 Y92:Y102" xr:uid="{CBD486C7-A5DB-48F1-B496-5027CC51E830}">
       <formula1>"CO,RO,SDO,LGU,SCHOOL"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X22:X30 X32:X42 X44:X54 X68:X78 X80:X90 X56:X66 X92:X102 R104:R114 X13:X20 X4:X11 L22:L30 L32:L42 L44:L54 L68:L78 L80:L90 L56:L66 L92:L102 L104:L114 L13:L20 L4:L11 R22:R30 R32:R42 R44:R54 R68:R78 R80:R90 R56:R66 R92:R102 F104:F114 R13:R20 R4:R11 F22:F30 F32:F42 F44:F54 F68:F78 F80:F90 F56:F66 F4:F11 F92:F102 X116:X123 F13:F20 F116:F123 R116:R123 L116:L123 X104:X114" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
-      <formula1>"2024,2025"</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F116:F123 F104:F114 F92:F102 F80:F90 F68:F78 F56:F66 F44:F54 F32:F42 F22:F30 F13:F20 F4:F11 L116:L123 L104:L114 L92:L102 L80:L90 L68:L78 L56:L66 L44:L54 L32:L42 L22:L30 L13:L20 L4:L11 R116:R123 R104:R114 R92:R102 R80:R90 R68:R78 R56:R66 R44:R54 R32:R42 R22:R30 R13:R20 R4:R11 X116:X123 X104:X114 X92:X102 X80:X90 X68:X78 X56:X66 X44:X54 X32:X42 X22:X30 X13:X20 X4:X11" xr:uid="{77F72D89-8371-4D0C-A323-BD25723C617C}">
+      <formula1>"2024,2025,2026"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
